--- a/vendor-report/FML CAT 6060.xlsx
+++ b/vendor-report/FML CAT 6060.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Permits\Kroonkantoor Dropbox\Tracking\CURRENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eicker FKT\Kroonkantoor Dropbox\Tracking\CURRENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8424BF0F-F81F-412C-950C-8C2ADFAE28F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765BE6A1-4AC8-47EF-9E0B-31BE44472CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB269D22-8FB6-40C6-A8E5-FB801ACD9DD5}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB269D22-8FB6-40C6-A8E5-FB801ACD9DD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="149">
   <si>
     <t>Load Desc.</t>
   </si>
@@ -445,6 +445,33 @@
   </si>
   <si>
     <t>Likasi</t>
+  </si>
+  <si>
+    <t>Kanyaka</t>
+  </si>
+  <si>
+    <t>Kasumbulesa border</t>
+  </si>
+  <si>
+    <t>Kolwezi</t>
+  </si>
+  <si>
+    <t>Connex Kolwezi</t>
+  </si>
+  <si>
+    <t>Kapolowe</t>
+  </si>
+  <si>
+    <t>Kasumbulesa border - DRC side</t>
+  </si>
+  <si>
+    <t>KCC</t>
+  </si>
+  <si>
+    <t>On site-Waiting to offload</t>
+  </si>
+  <si>
+    <t>Offloaded</t>
   </si>
 </sst>
 </file>
@@ -2035,69 +2062,175 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
+    <row r="32" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>46194</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+    <row r="36" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
